--- a/output_powerbi/dim_sedi_esistenti.xlsx
+++ b/output_powerbi/dim_sedi_esistenti.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,92 +429,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SedeID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TipoPunto</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tipologia</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>STATO PDV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Rag. Sociale</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Codice Agenzia</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Codici FR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Indirizzo</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Comune</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>CAP</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Regione</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Sede Operativa SUP</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Latitudine</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Longitudine</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Stato_Geocoding</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Precisione_Geocoding</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>OrigineCoordinate</t>
         </is>
@@ -583,7 +595,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -665,7 +681,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -747,7 +767,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -829,7 +853,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -911,7 +939,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -993,7 +1025,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1071,7 +1107,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1153,7 +1193,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1235,7 +1279,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1317,7 +1365,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1399,7 +1451,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1481,7 +1537,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1563,7 +1623,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1645,7 +1709,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1727,7 +1795,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1809,7 +1881,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1891,7 +1967,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -1969,7 +2049,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -2047,7 +2131,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -2129,7 +2217,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -2211,7 +2303,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -2457,7 +2553,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -2539,7 +2639,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -2617,7 +2721,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -2699,7 +2807,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -2781,7 +2893,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -2863,7 +2979,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -2941,7 +3061,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -3023,7 +3147,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -3105,7 +3233,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -3273,7 +3405,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -3355,7 +3491,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -3437,7 +3577,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -3519,7 +3663,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -3597,7 +3745,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -3675,7 +3827,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -3757,7 +3913,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -3835,7 +3995,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -3913,7 +4077,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -3995,7 +4163,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -4245,7 +4417,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -4327,7 +4503,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -4409,7 +4589,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -4491,7 +4675,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -4573,7 +4761,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -4655,7 +4847,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R52" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -4737,7 +4933,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -4819,7 +5019,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -4987,7 +5191,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -5069,7 +5277,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -5151,7 +5363,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -5233,7 +5449,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R59" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -5315,7 +5535,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -5397,7 +5621,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R61" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -5479,7 +5707,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R62" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -5561,7 +5793,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R63" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -5643,7 +5879,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R64" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -5725,7 +5965,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R65" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -5807,7 +6051,11 @@
           <t>TROVATO_FALLBACK</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R66" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -5889,7 +6137,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R67" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -5971,7 +6223,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R68" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -6053,7 +6309,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R69" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -6131,7 +6391,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R70" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -6209,7 +6473,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R71" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -6287,7 +6555,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R72" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -6365,7 +6637,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R73" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -6443,7 +6719,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R74" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -6521,7 +6801,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R75" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -6599,7 +6883,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -6677,7 +6965,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R77" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -6755,7 +7047,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R78" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -6833,7 +7129,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R79" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -6911,7 +7211,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R80" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -6989,7 +7293,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R81" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -7067,7 +7375,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R82" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -7145,7 +7457,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R83" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -7223,7 +7539,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R84" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -7305,7 +7625,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R85" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -7383,7 +7707,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R86" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -7465,7 +7793,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R87" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -7547,7 +7879,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R88" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -7629,7 +7965,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R89" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -7711,7 +8051,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R90" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -7793,7 +8137,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R91" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -7875,7 +8223,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R92" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -7957,7 +8309,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R93" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8039,7 +8395,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R94" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8121,7 +8481,11 @@
           <t>TROVATO_FALLBACK</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R95" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8203,7 +8567,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R96" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8281,7 +8649,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R97" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8359,7 +8731,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R98" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8437,7 +8813,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R99" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8519,7 +8899,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R100" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8601,7 +8985,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R101" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8683,7 +9071,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R102" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8761,7 +9153,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R103" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8839,7 +9235,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R104" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8917,7 +9317,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R105" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -8999,7 +9403,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R106" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -9081,7 +9489,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R107" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -9163,7 +9575,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R108" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -9245,7 +9661,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R109" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -9327,7 +9747,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R110" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -9405,7 +9829,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R111" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -9479,7 +9907,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R112" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -9557,7 +9989,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R113" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -9635,7 +10071,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R114" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -9713,7 +10153,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R115" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -9791,7 +10235,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R116" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -9873,7 +10321,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R117" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -9951,7 +10403,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R118" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -10033,7 +10489,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R119" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -10115,7 +10575,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R120" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -10197,7 +10661,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R121" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -10279,7 +10747,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R122" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -10361,7 +10833,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R123" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -10443,7 +10919,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R124" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -10525,7 +11005,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R125" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -10607,7 +11091,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R126" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -10689,7 +11177,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R127" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -10771,7 +11263,11 @@
           <t>TROVATO_FALLBACK</t>
         </is>
       </c>
-      <c r="Q128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R128" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -10853,7 +11349,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R129" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -10935,7 +11435,11 @@
           <t>TROVATO_FALLBACK</t>
         </is>
       </c>
-      <c r="Q130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R130" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -11017,7 +11521,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R131" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -11099,7 +11607,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R132" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -11181,7 +11693,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R133" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -11263,7 +11779,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R134" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -11345,7 +11865,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R135" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -11427,7 +11951,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R136" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -11509,7 +12037,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R137" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -11591,7 +12123,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R138" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -11673,7 +12209,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R139" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -11755,7 +12295,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R140" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -11837,7 +12381,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R141" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -11919,7 +12467,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R142" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -11997,7 +12549,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R143" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -12075,7 +12631,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R144" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -12157,7 +12717,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R145" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -12235,7 +12799,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R146" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -12317,7 +12885,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R147" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -12395,7 +12967,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R148" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -12473,7 +13049,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R149" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -12551,7 +13131,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R150" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -12633,7 +13217,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R151" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -12711,7 +13299,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R152" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -12785,7 +13377,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R153" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -12867,7 +13463,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R154" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -12949,7 +13549,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R155" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13031,7 +13635,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R156" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13113,7 +13721,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R157" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -13191,7 +13803,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R158" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13269,7 +13885,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R159" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13347,7 +13967,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R160" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13429,7 +14053,11 @@
           <t>TROVATO_FALLBACK</t>
         </is>
       </c>
-      <c r="Q161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R161" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13511,7 +14139,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R162" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13593,7 +14225,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R163" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13675,7 +14311,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R164" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13757,7 +14397,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R165" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13835,7 +14479,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R166" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13917,7 +14565,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R167" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -13995,7 +14647,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R168" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -14073,7 +14729,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R169" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -14233,7 +14893,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R171" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -14311,7 +14975,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R172" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -14389,7 +15057,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R173" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -14467,7 +15139,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R174" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -14545,7 +15221,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R175" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -14627,7 +15307,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R176" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -14705,7 +15389,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R177" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -14783,7 +15471,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R178" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -14865,7 +15557,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R179" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -14947,7 +15643,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R180" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -15029,7 +15729,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R181" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -15107,7 +15811,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R182" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -15189,7 +15897,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R183" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -15267,7 +15979,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R184" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -15349,7 +16065,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R185" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -15431,7 +16151,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R186" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -15513,7 +16237,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R187" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -15595,7 +16323,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R188" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -15677,7 +16409,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R189" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -15755,7 +16491,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R190" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -15833,7 +16573,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R191" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -15915,7 +16659,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R192" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -15993,7 +16741,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R193" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -16071,7 +16823,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R194" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -16149,7 +16905,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R195" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -16227,7 +16987,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R196" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -16305,7 +17069,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R197" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -16383,7 +17151,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R198" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -16461,7 +17233,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R199" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -16543,7 +17319,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R200" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -16625,7 +17405,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R201" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -16707,7 +17491,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R202" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -16789,7 +17577,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R203" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -16871,7 +17663,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R204" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -16953,7 +17749,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R205" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17031,7 +17831,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R206" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17113,7 +17917,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R207" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17195,7 +18003,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R208" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17277,7 +18089,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R209" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17355,7 +18171,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R210" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17433,7 +18253,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R211" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17507,7 +18331,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R212" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17585,7 +18413,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R213" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17753,7 +18585,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R215" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17835,7 +18671,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R216" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17913,7 +18753,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R217" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -17991,7 +18835,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R218" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -18073,7 +18921,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R219" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -18155,7 +19007,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R220" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -18233,7 +19089,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R221" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -18315,7 +19175,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R222" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -18397,7 +19261,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R223" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -18479,7 +19347,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R224" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -18561,7 +19433,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R225" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -18643,7 +19519,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R226" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -18725,7 +19605,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R227" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -18803,7 +19687,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R228" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -18877,7 +19765,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R229" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -18955,7 +19847,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R230" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -19037,7 +19933,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R231" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -19115,7 +20015,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R232" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -19197,7 +20101,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R233" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -19275,7 +20183,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R234" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -19353,7 +20265,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R235" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -19435,7 +20351,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R236" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -19509,7 +20429,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R237" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -19591,7 +20515,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R238" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -19669,7 +20597,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R239" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -19751,7 +20683,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R240" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -19829,7 +20765,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R241" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -19911,7 +20851,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R242" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -19993,7 +20937,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R243" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -20075,7 +21023,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R244" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -20235,7 +21187,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R246" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -20313,7 +21269,11 @@
           <t>TROVATO_FALLBACK</t>
         </is>
       </c>
-      <c r="Q247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R247" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -20481,7 +21441,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R249" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -20563,7 +21527,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q250" t="inlineStr"/>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R250" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -20641,7 +21609,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R251" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -20715,7 +21687,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R252" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -20789,7 +21765,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R253" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -20863,7 +21843,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R254" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -20945,7 +21929,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R255" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21023,7 +22011,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R256" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21097,7 +22089,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R257" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21171,7 +22167,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R258" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21249,7 +22249,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R259" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21331,7 +22335,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R260" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21409,7 +22417,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R261" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21487,7 +22499,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R262" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21569,7 +22585,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R263" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21651,7 +22671,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R264" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -21733,7 +22757,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R265" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21815,7 +22843,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R266" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21893,7 +22925,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R267" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -21975,7 +23011,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R268" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -22057,7 +23097,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q269" t="inlineStr"/>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R269" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -22135,7 +23179,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R270" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -22213,7 +23261,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R271" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -22295,7 +23347,11 @@
           <t>NON_TROVATO</t>
         </is>
       </c>
-      <c r="Q272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R272" t="inlineStr">
         <is>
           <t>Copilot</t>
@@ -22369,7 +23425,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R273" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -22451,7 +23511,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R274" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -22533,7 +23597,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q275" t="inlineStr"/>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R275" t="inlineStr">
         <is>
           <t>Nominatim</t>
@@ -22615,7 +23683,11 @@
           <t>TROVATO</t>
         </is>
       </c>
-      <c r="Q276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="R276" t="inlineStr">
         <is>
           <t>Nominatim</t>
